--- a/output/output_ZE02-133.xlsx
+++ b/output/output_ZE02-133.xlsx
@@ -413,118 +413,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC112"/>
+  <dimension ref="A1:AC111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>員数</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Unnamed: 1</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Unnamed: 2</t>
+          <t>Ｂ</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Unnamed: 3</t>
+          <t>Ａ</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>分番</t>
+          <t>DIV. No</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>納番</t>
+          <t>SPLY No</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>部署</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>ITEM No.</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>SY</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>DWG.No.</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>NAME OF PART</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Unnamed: 12</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>MATERIAL      CODE</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>摘    要                                   SUMMARY</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ミスミ品も自家にて全て購入すること。</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>素材    MATL</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>仕上    FIN.</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>図　番</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>番号</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>記号</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>図番</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>部品名</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>検ｺ</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Unnamed: 12</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>資材ｺ-ﾄﾞ</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>材質材料                            MATERIAL</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>品# 1-3 は先発 仕#4711 引当（マニホルド電磁弁:仕様書付）</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>重量(Kg)       MASS</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Unnamed: 17</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Unnamed: 18</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Unnamed: 19</t>
-        </is>
-      </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Unnamed: 20</t>
+          <t>Rev</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Unnamed: 21</t>
+          <t>消耗品</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
@@ -534,22 +534,22 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>購入品(単価)</t>
+          <t>Unnamed: 23</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>購入品(小計)</t>
+          <t>Unnamed: 24</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>製作品(単価)</t>
+          <t>Unnamed: 25</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>製作品(小計)</t>
+          <t>(k\)</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
@@ -564,120 +564,68 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ｄ</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Ｃ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ｂ</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ａ</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DIV. No</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>SPLY No</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>SHOP</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ITEM No.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>SY</t>
-        </is>
-      </c>
+          <t>09A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>DWG.No.</t>
+          <t>E1DE01329</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>NAME OF PART</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>IC</t>
-        </is>
-      </c>
+          <t>UNIT-A</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>MATERIAL      CODE</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>摘    要                                   SUMMARY</t>
+          <t>チップ送出し</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ミスミ品も自家にて全て購入すること。</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>素材    MATL</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>仕上    FIN.</t>
-        </is>
-      </c>
+          <t>E1ZE01308</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>図　番</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>番号</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Rev</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>消耗品</t>
-        </is>
-      </c>
+          <t>E1ZE02-133</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>(k\)</t>
-        </is>
+      <c r="AA2" t="n">
+        <v>606.371</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
@@ -693,25 +641,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>09A</t>
+          <t>09B</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
+      <c r="H3" t="n">
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>E1DE01329</t>
+          <t>E1DG02163</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>UNIT-A</t>
+          <t>CAMRA-A</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -719,12 +665,12 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>チップ送出し</t>
+          <t>チップ青点･マジック検査</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>E1ZE01308</t>
+          <t>E1ZG03476</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -734,23 +680,17 @@
           <t>E1ZE02-133</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
+      <c r="T3" t="n">
         <v>2</v>
       </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="n">
-        <v>606.371</v>
-      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2510.02</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -766,25 +706,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>09B</t>
+          <t>09C</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
+      <c r="H4" t="n">
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>E1DG02163</t>
+          <t>E1DE01331</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CAMRA-A</t>
+          <t>DRIV-A</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -792,12 +730,12 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>チップ青点･マジック検査</t>
+          <t>チップピッチ送り</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>E1ZG03476</t>
+          <t>E1ZE01313</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -807,21 +745,17 @@
           <t>E1ZE02-133</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
+      <c r="T4" t="n">
+        <v>3</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="n">
-        <v>2510.02</v>
-      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>528.866</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -837,25 +771,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>09C</t>
+          <t>09D</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="H5" t="n">
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>E1DE01331</t>
+          <t>E1DE01332</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>DRIV-A</t>
+          <t>PUSHR-A</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -863,12 +795,12 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>チップピッチ送り</t>
+          <t>チップ押え</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>E1ZE01313</t>
+          <t>E1ZE01316</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -878,24 +810,24 @@
           <t>E1ZE02-133</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="T5" t="n">
+        <v>4</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="n">
-        <v>528.866</v>
-      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>115.212</v>
       </c>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>SHH511957</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -908,25 +840,23 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>09D</t>
+          <t>09E</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+      <c r="H6" t="n">
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>E1DE01332</t>
+          <t>E1DE01333</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>PUSHR-A</t>
+          <t>UNIT-A</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -934,12 +864,12 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>チップ押え</t>
+          <t>チップ移載</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>E1ZE01316</t>
+          <t>E1ZE01317</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -949,26 +879,22 @@
           <t>E1ZE02-133</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+      <c r="T6" t="n">
+        <v>5</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
-        <v>115.212</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>188.469</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>SHH511957</t>
+          <t>SHH215398</t>
         </is>
       </c>
     </row>
@@ -983,20 +909,18 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>09E</t>
+          <t>09F</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
+      <c r="H7" t="n">
+        <v>6</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>E1DE01333</t>
+          <t>E1DE01334</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1009,12 +933,12 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>チップ移載</t>
+          <t>チップエスケープ</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>E1ZE01317</t>
+          <t>E1ZE01319</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1024,26 +948,22 @@
           <t>E1ZE02-133</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
+      <c r="T7" t="n">
+        <v>6</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="n">
-        <v>188.469</v>
-      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>221.736</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>SHH215398</t>
+          <t>SHH511494</t>
         </is>
       </c>
     </row>
@@ -1058,25 +978,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>09F</t>
+          <t>09G</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="H8" t="n">
+        <v>7</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>E1DE01334</t>
+          <t>E1FE00762</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>UNIT-A</t>
+          <t>CUT-A</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1084,12 +1002,12 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>チップエスケープ</t>
+          <t>チップカット</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>E1ZE01319</t>
+          <t>E1ZE01321</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1099,26 +1017,22 @@
           <t>E1ZE02-133</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="T8" t="n">
+        <v>7</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="n">
-        <v>221.736</v>
-      </c>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>SHH511494</t>
+          <t>SHH215390</t>
         </is>
       </c>
     </row>
@@ -1133,25 +1047,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>09G</t>
+          <t>09H</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="H9" t="n">
+        <v>8</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>E1FE00762</t>
+          <t>E1DE01335</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>CUT-A</t>
+          <t>CUT.D-A</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1159,12 +1071,12 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>チップカット</t>
+          <t>チップカッタ駆動</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>E1ZE01321</t>
+          <t>E1ZE01322</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1174,26 +1086,22 @@
           <t>E1ZE02-133</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="T9" t="n">
+        <v>8</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="n">
-        <v>150</v>
-      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>160.78</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>SHH215390</t>
+          <t>SHH215391</t>
         </is>
       </c>
     </row>
@@ -1208,25 +1116,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>09H</t>
+          <t>09I</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="H10" t="n">
+        <v>9</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>E1DE01335</t>
+          <t>E1DE01336</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>CUT.D-A</t>
+          <t>UNIT-A</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1234,12 +1140,12 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>チップカッタ駆動</t>
+          <t>チップ供給フレーム</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>E1ZE01322</t>
+          <t>E1ZE01323</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1249,18 +1155,14 @@
           <t>E1ZE02-133</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="T10" t="n">
+        <v>9</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="n">
-        <v>160.78</v>
-      </c>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1268,7 +1170,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>SHH215391</t>
+          <t>SHH512030</t>
         </is>
       </c>
     </row>
@@ -1283,20 +1185,18 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>09I</t>
+          <t>09J</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
+      <c r="H11" t="n">
+        <v>10</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>E1DE01336</t>
+          <t>E1FE00763</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1309,12 +1209,12 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>チップ供給フレーム</t>
+          <t>チップ除塵</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>E1ZE01323</t>
+          <t>E1ZE01325</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -1324,10 +1224,8 @@
           <t>E1ZE02-133</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
+      <c r="T11" t="n">
+        <v>10</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
@@ -1336,12 +1234,12 @@
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>150.17</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>SHH512030</t>
+          <t>SHH</t>
         </is>
       </c>
     </row>
@@ -1356,25 +1254,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>09J</t>
+          <t>09K</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="H12" t="n">
+        <v>11</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>E1FE00763</t>
+          <t>E1DE02041</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>UNIT-A</t>
+          <t>TB-A</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1382,12 +1278,12 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>チップ除塵</t>
+          <t>チップ供給テーブル</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>E1ZE01325</t>
+          <t>E1ZE01421</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -1398,25 +1294,19 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="n">
-        <v>150.17</v>
-      </c>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>508.456</v>
       </c>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>SHH</t>
-        </is>
-      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1429,25 +1319,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>09K</t>
+          <t>09L</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="H13" t="n">
+        <v>12</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>E1DE02041</t>
+          <t>E1DE01338</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>TB-A</t>
+          <t>SHUTE-A</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1455,12 +1343,12 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>チップ供給テーブル</t>
+          <t>チップNG排出</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>E1ZE01421</t>
+          <t>E1ZE01328</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -1471,18 +1359,16 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="n">
-        <v>508.456</v>
-      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
@@ -1491,47 +1377,21 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>09L</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="H14" t="n">
+        <v>13</v>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>E1DE01338</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>SHUTE-A</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>チップNG排出</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>E1ZE01328</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
@@ -1540,19 +1400,17 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
     </row>
@@ -1560,23 +1418,45 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="H15" t="n">
+        <v>14</v>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>E1DE01381</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>UNIT-A</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>フープ材送出し</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>E1ZE01424</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
@@ -1585,17 +1465,17 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>1257.971</v>
+      </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
     </row>
@@ -1610,25 +1490,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="H16" t="n">
+        <v>15</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>E1DE01381</t>
+          <t>E1FE00764</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>UNIT-A</t>
+          <t>SENSR-A</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1636,12 +1514,12 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>フープ材送出し</t>
+          <t>フープ材送出しセンサ部</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>E1ZE01424</t>
+          <t>E1ZE01334</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -1652,18 +1530,16 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="n">
-        <v>1257.971</v>
-      </c>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>145.63</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -1679,25 +1555,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="H17" t="n">
+        <v>16</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E1FE00764</t>
+          <t>E1FE01298</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>SENSR-A</t>
+          <t>GUIDE-A</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1705,12 +1579,12 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>フープ材送出しセンサ部</t>
+          <t>フープ材中間ガイド</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>E1ZE01334</t>
+          <t>E1ZE01426</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
@@ -1721,18 +1595,16 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="n">
-        <v>145.63</v>
-      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -1748,25 +1620,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>10D</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="H18" t="n">
+        <v>17</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>E1FE01298</t>
+          <t>E1DE02045</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>GUIDE-A</t>
+          <t>DRIV-A</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1774,12 +1644,12 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>フープ材中間ガイド</t>
+          <t>フープ材ピッチ送り</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>E1ZE01426</t>
+          <t>E1ZE01427</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -1790,18 +1660,16 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="n">
-        <v>300</v>
-      </c>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1268.672</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -1817,25 +1685,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10D</t>
+          <t>10E</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="H19" t="n">
+        <v>18</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>E1DE02045</t>
+          <t>E1FE01299</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>DRIV-A</t>
+          <t>CUT-A</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1843,12 +1709,12 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>フープ材ピッチ送り</t>
+          <t>フープ材カット</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>E1ZE01427</t>
+          <t>E1ZE02064</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -1859,18 +1725,16 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="n">
-        <v>1268.672</v>
-      </c>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1438.072</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -1886,25 +1750,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10E</t>
+          <t>10F</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="H20" t="n">
+        <v>19</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>E1FE01299</t>
+          <t>E1DE01342</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>CUT-A</t>
+          <t>DRAW-A</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1912,12 +1774,12 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>フープ材カット</t>
+          <t>フープ材引出し</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>E1ZE02064</t>
+          <t>E1ZE01341</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
@@ -1928,18 +1790,16 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="n">
-        <v>1438.072</v>
-      </c>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>162.71</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -1955,25 +1815,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10F</t>
+          <t>10G</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="H21" t="n">
+        <v>20</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>E1DE01342</t>
+          <t>E1DE02059</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>DRAW-A</t>
+          <t>HNDLR-A</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1981,12 +1839,12 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>フープ材引出し</t>
+          <t>チップ・フープ材挿入</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>E1ZE01341</t>
+          <t>E1ZE01429</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
@@ -1997,18 +1855,16 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="n">
-        <v>162.71</v>
-      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1040.37</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
@@ -2024,25 +1880,23 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10G</t>
+          <t>11A</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="H22" t="n">
+        <v>21</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>E1DE02059</t>
+          <t>E1FE00323</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>HNDLR-A</t>
+          <t>P.F</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2050,12 +1904,12 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>チップ・フープ材挿入</t>
+          <t>マウントパーツフィーダ:1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>E1ZE01429</t>
+          <t>(400901,CA)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
@@ -2066,18 +1920,16 @@
         </is>
       </c>
       <c r="T22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="n">
-        <v>1040.37</v>
-      </c>
+      <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1265.54</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
@@ -2093,20 +1945,18 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11A</t>
+          <t>11B</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="H23" t="n">
+        <v>22</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>E1FE00323</t>
+          <t>E1FE00324</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2119,12 +1969,12 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>マウントパーツフィーダ:1</t>
+          <t>マウントパーツフィーダ:2</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>(400901,CA)</t>
+          <t>(400902,CA)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
@@ -2135,18 +1985,16 @@
         </is>
       </c>
       <c r="T23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="n">
-        <v>1265.54</v>
-      </c>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
@@ -2162,25 +2010,23 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11B</t>
+          <t>11C</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="H24" t="n">
+        <v>23</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>E1FE00324</t>
+          <t>E1DE01344</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>P.F</t>
+          <t>SENSR-A</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -2188,12 +2034,12 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>マウントパーツフィーダ:2</t>
+          <t>マウント到達検出:1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>(400902,CA)</t>
+          <t>E1ZE01348</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
@@ -2204,18 +2050,16 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="n">
-        <v>1260</v>
-      </c>
+      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>349.694</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
@@ -2231,20 +2075,18 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11C</t>
+          <t>11D</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="H25" t="n">
+        <v>24</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>E1DE01344</t>
+          <t>E1DE01345</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2257,12 +2099,12 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>マウント到達検出:1</t>
+          <t>マウント到達検出:2</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>E1ZE01348</t>
+          <t>E1ZE01349</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
@@ -2273,18 +2115,16 @@
         </is>
       </c>
       <c r="T25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="n">
-        <v>349.694</v>
-      </c>
+      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>249.694</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
@@ -2300,25 +2140,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11D</t>
+          <t>11E</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="H26" t="n">
+        <v>25</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>E1DE01345</t>
+          <t>E1DE01346</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>SENSR-A</t>
+          <t>UNIT-A</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2326,12 +2164,12 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>マウント到達検出:2</t>
+          <t>マウント表裏反転:1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>E1ZE01349</t>
+          <t>E1ZE01350</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
@@ -2342,18 +2180,16 @@
         </is>
       </c>
       <c r="T26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="n">
-        <v>249.694</v>
-      </c>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>303.586</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
@@ -2369,20 +2205,18 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11E</t>
+          <t>11F</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="H27" t="n">
+        <v>26</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>E1DE01346</t>
+          <t>E1DE01347</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2395,12 +2229,12 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>マウント表裏反転:1</t>
+          <t>マウント表裏反転:2</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>E1ZE01350</t>
+          <t>E1ZE01352</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
@@ -2411,18 +2245,16 @@
         </is>
       </c>
       <c r="T27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="n">
-        <v>303.586</v>
-      </c>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>279.49</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
@@ -2438,25 +2270,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11F</t>
+          <t>11G</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="H28" t="n">
+        <v>27</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>E1DE01347</t>
+          <t>E1DE01348</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>UNIT-A</t>
+          <t>HNDLR-A</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2464,12 +2294,12 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>マウント表裏反転:2</t>
+          <t>マウント供給スライド排出:1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>E1ZE01352</t>
+          <t>E1ZE01354</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
@@ -2480,18 +2310,16 @@
         </is>
       </c>
       <c r="T28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="n">
-        <v>279.49</v>
-      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>815.016</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
@@ -2507,20 +2335,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11G</t>
+          <t>11H</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="H29" t="n">
+        <v>28</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>E1DE01348</t>
+          <t>E1DE01349</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2533,12 +2359,12 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>マウント供給スライド排出:1</t>
+          <t>マウント供給スライド排出:2</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>E1ZE01354</t>
+          <t>E1ZE01357</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
@@ -2549,18 +2375,16 @@
         </is>
       </c>
       <c r="T29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="n">
-        <v>815.016</v>
-      </c>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>794.8099999999999</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
@@ -2576,25 +2400,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11H</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="H30" t="n">
+        <v>29</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>E1DE01349</t>
+          <t>E1DE02042</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>HNDLR-A</t>
+          <t>TB-A</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2602,12 +2424,12 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>マウント供給スライド排出:2</t>
+          <t>組立テーブル:1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>E1ZE01357</t>
+          <t>E1ZE01422</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
@@ -2618,18 +2440,16 @@
         </is>
       </c>
       <c r="T30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="n">
-        <v>794.8099999999999</v>
-      </c>
+      <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>851.0839999999999</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
@@ -2645,20 +2465,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12A</t>
+          <t>12B</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="H31" t="n">
+        <v>30</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>E1DE02042</t>
+          <t>E1DE02043</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2671,12 +2489,12 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>組立テーブル:1</t>
+          <t>組立テーブル:2</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>E1ZE01422</t>
+          <t>E1ZE01423</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
@@ -2687,18 +2505,16 @@
         </is>
       </c>
       <c r="T31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="n">
-        <v>851.0839999999999</v>
-      </c>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>811.394</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
@@ -2714,25 +2530,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12B</t>
+          <t>12C</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="H32" t="n">
+        <v>31</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>E1DE02043</t>
+          <t>E1FG01501</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>TB-A</t>
+          <t>SENSR-A</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2740,12 +2554,12 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>組立テーブル:2</t>
+          <t>組立テーブルセンサ取付:1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>E1ZE01423</t>
+          <t>E1ZG03479</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
@@ -2756,18 +2570,16 @@
         </is>
       </c>
       <c r="T32" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="n">
-        <v>811.394</v>
-      </c>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>128.628</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
@@ -2783,20 +2595,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12C</t>
+          <t>12D</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="H33" t="n">
+        <v>32</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>E1FG01501</t>
+          <t>E1FG01502</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2809,12 +2619,12 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>組立テーブルセンサ取付:1</t>
+          <t>組立テーブルセンサ取付:2</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>E1ZG03479</t>
+          <t>E1ZG03480</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
@@ -2825,18 +2635,16 @@
         </is>
       </c>
       <c r="T33" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="n">
-        <v>128.628</v>
-      </c>
+      <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>115.985</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
@@ -2852,25 +2660,23 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12D</t>
+          <t>12E</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="H34" t="n">
+        <v>33</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>E1FG01502</t>
+          <t>E1FE00770</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SENSR-A</t>
+          <t>WLDR-A</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2878,12 +2684,12 @@
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>組立テーブルセンサ取付:2</t>
+          <t>溶着機固定:1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>E1ZG03480</t>
+          <t>E1ZE01366</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr"/>
@@ -2894,18 +2700,16 @@
         </is>
       </c>
       <c r="T34" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="n">
-        <v>115.985</v>
-      </c>
+      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>200.45</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
@@ -2921,20 +2725,18 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12E</t>
+          <t>12F</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="H35" t="n">
+        <v>34</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>E1FE00770</t>
+          <t>E1FE00771</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2947,12 +2749,12 @@
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>溶着機固定:1</t>
+          <t>溶着機固定:2</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>E1ZE01366</t>
+          <t>E1ZE01367</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr"/>
@@ -2963,18 +2765,16 @@
         </is>
       </c>
       <c r="T35" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="n">
-        <v>200.45</v>
-      </c>
+      <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>200.45</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
@@ -2990,25 +2790,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12F</t>
+          <t>12G</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="H36" t="n">
+        <v>35</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>E1FE00771</t>
+          <t>E1DE01353</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>WLDR-A</t>
+          <t>UNIT-A</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -3016,12 +2814,12 @@
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>溶着機固定:2</t>
+          <t>マウント位置決め:1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>E1ZE01367</t>
+          <t>E1ZE01368</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr"/>
@@ -3032,18 +2830,16 @@
         </is>
       </c>
       <c r="T36" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="n">
-        <v>200.45</v>
-      </c>
+      <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>212.51</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
@@ -3059,20 +2855,18 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12G</t>
+          <t>12H</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="H37" t="n">
+        <v>36</v>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>E1DE01353</t>
+          <t>E1DE01354</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3085,12 +2879,12 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>マウント位置決め:1</t>
+          <t>マウント位置決め:2</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>E1ZE01368</t>
+          <t>E1ZE01370</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr"/>
@@ -3101,18 +2895,16 @@
         </is>
       </c>
       <c r="T37" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="n">
-        <v>212.51</v>
-      </c>
+      <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>203.01</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
@@ -3128,25 +2920,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12H</t>
+          <t>12I</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="H38" t="n">
+        <v>37</v>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>E1DE01354</t>
+          <t>E1DG02166</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>UNIT-A</t>
+          <t>CAMRA-A</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -3154,12 +2944,12 @@
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>マウント位置決め:2</t>
+          <t>2Dコード印字検査:1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>E1ZE01370</t>
+          <t>E1ZG03481</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr"/>
@@ -3170,18 +2960,16 @@
         </is>
       </c>
       <c r="T38" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="n">
-        <v>203.01</v>
-      </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>196.8</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
@@ -3197,20 +2985,18 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12I</t>
+          <t>12J</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="H39" t="n">
+        <v>38</v>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>E1DG02166</t>
+          <t>E1DG02167</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3223,12 +3009,12 @@
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2Dコード印字検査:1</t>
+          <t>2Dコード印字検査:2</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>E1ZG03481</t>
+          <t>E1ZG03482</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr"/>
@@ -3239,18 +3025,16 @@
         </is>
       </c>
       <c r="T39" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="n">
-        <v>196.8</v>
-      </c>
+      <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>196.8</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
@@ -3266,25 +3050,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12J</t>
+          <t>12K</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="H40" t="n">
+        <v>39</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>E1DG02167</t>
+          <t>E1DE01357</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>CAMRA-A</t>
+          <t>UNIT-A</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -3292,12 +3074,12 @@
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2Dコード印字検査:2</t>
+          <t>スライド180ﾟ反転:1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>E1ZG03482</t>
+          <t>E1ZE01374</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr"/>
@@ -3308,18 +3090,16 @@
         </is>
       </c>
       <c r="T40" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="n">
-        <v>196.8</v>
-      </c>
+      <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>203.44</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
@@ -3335,20 +3115,18 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12K</t>
+          <t>12L</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="H41" t="n">
+        <v>40</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>E1DE01357</t>
+          <t>E1DE01358</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3361,12 +3139,12 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>スライド180ﾟ反転:1</t>
+          <t>スライド180ﾟ反転:2</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>E1ZE01374</t>
+          <t>E1ZE01376</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
@@ -3377,18 +3155,16 @@
         </is>
       </c>
       <c r="T41" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="n">
-        <v>203.44</v>
-      </c>
+      <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>203.44</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
@@ -3404,25 +3180,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12L</t>
+          <t>13A</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="H42" t="n">
+        <v>41</v>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>E1DE01358</t>
+          <t>E1DE01359</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>UNIT-A</t>
+          <t>CNVR-A</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3430,12 +3204,12 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>スライド180ﾟ反転:2</t>
+          <t>スライド搬送コンベヤ</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>E1ZE01376</t>
+          <t>E1ZE01378</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
@@ -3446,18 +3220,16 @@
         </is>
       </c>
       <c r="T42" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="n">
-        <v>203.44</v>
-      </c>
+      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1020.39</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
@@ -3473,25 +3245,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13A</t>
+          <t>13B</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="H43" t="n">
+        <v>42</v>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>E1DE01359</t>
+          <t>E1DE02111</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>CNVR-A</t>
+          <t>HNDLR-A</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -3499,12 +3269,12 @@
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>スライド搬送コンベヤ</t>
+          <t>スライド移載</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>E1ZE01378</t>
+          <t>E1ZE02111</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr"/>
@@ -3515,18 +3285,16 @@
         </is>
       </c>
       <c r="T43" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="n">
-        <v>1020.39</v>
-      </c>
+      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>236.63</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
@@ -3542,25 +3310,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13B</t>
+          <t>13C</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="H44" t="n">
+        <v>43</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>E1DE02111</t>
+          <t>E1DE02189</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>HNDLR-A</t>
+          <t>RAIL-A</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3568,12 +3334,12 @@
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>スライド移載</t>
+          <t>搬送面</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>E1ZE02111</t>
+          <t>E1ZE02157</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr"/>
@@ -3584,18 +3350,16 @@
         </is>
       </c>
       <c r="T44" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="n">
-        <v>236.63</v>
-      </c>
+      <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>301.28</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
@@ -3611,25 +3375,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13C</t>
+          <t>13D</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="H45" t="n">
+        <v>44</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>E1DE02189</t>
+          <t>E1DE01362</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>RAIL-A</t>
+          <t>SAO-A</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3637,12 +3399,12 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>搬送面</t>
+          <t>サオ送り</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>E1ZE02157</t>
+          <t>E1ZE01384</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr"/>
@@ -3653,18 +3415,16 @@
         </is>
       </c>
       <c r="T45" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="n">
-        <v>301.28</v>
-      </c>
+      <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>344.734</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
@@ -3680,25 +3440,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13D</t>
+          <t>13E</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="H46" t="n">
+        <v>45</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>E1DE01362</t>
+          <t>E1DG02164</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SAO-A</t>
+          <t>CAMRA-A</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3706,12 +3464,12 @@
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>サオ送り</t>
+          <t>総合検査 B</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>E1ZE01384</t>
+          <t>E1ZG03477</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr"/>
@@ -3722,18 +3480,16 @@
         </is>
       </c>
       <c r="T46" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="n">
-        <v>344.734</v>
-      </c>
+      <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>152.22</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
@@ -3749,25 +3505,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>13E</t>
+          <t>13F</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="H47" t="n">
+        <v>46</v>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>E1DG02164</t>
+          <t>E1DE01365</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>CAMRA-A</t>
+          <t>PRINT-A</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3775,12 +3529,12 @@
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>総合検査 B</t>
+          <t>印字部</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>E1ZG03477</t>
+          <t>E1ZE01388</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr"/>
@@ -3791,18 +3545,16 @@
         </is>
       </c>
       <c r="T47" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="n">
-        <v>152.22</v>
-      </c>
+      <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>154.028</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
@@ -3818,25 +3570,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13F</t>
+          <t>13G</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="H48" t="n">
+        <v>47</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>E1DE01365</t>
+          <t>E1DE02160</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>PRINT-A</t>
+          <t>CAMRA-A</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3844,12 +3594,12 @@
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>印字部</t>
+          <t>総合検査 A</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>E1ZE01388</t>
+          <t>E1ZE02136</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr"/>
@@ -3860,18 +3610,16 @@
         </is>
       </c>
       <c r="T48" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="n">
-        <v>154.028</v>
-      </c>
+      <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>341.4</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr"/>
@@ -3887,25 +3635,23 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13G</t>
+          <t>13H</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="H49" t="n">
+        <v>48</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>E1DE02160</t>
+          <t>E1DE01367</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>CAMRA-A</t>
+          <t>SHUTE-A</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3913,12 +3659,12 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>総合検査 A</t>
+          <t>NG排出</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>E1ZE02136</t>
+          <t>E1ZE01394</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr"/>
@@ -3929,18 +3675,16 @@
         </is>
       </c>
       <c r="T49" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="n">
-        <v>341.4</v>
-      </c>
+      <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
@@ -3956,25 +3700,23 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>13H</t>
+          <t>13I</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="H50" t="n">
+        <v>49</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>E1DE01367</t>
+          <t>E1FE00772</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>SHUTE-A</t>
+          <t>UNIT-A</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3982,12 +3724,12 @@
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>NG排出</t>
+          <t>表裏判別／除塵部</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>E1ZE01394</t>
+          <t>E1ZE01395</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr"/>
@@ -3998,18 +3740,16 @@
         </is>
       </c>
       <c r="T50" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="n">
-        <v>200</v>
-      </c>
+      <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>374.444</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
@@ -4018,47 +3758,21 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>13I</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="H51" t="n">
+        <v>50</v>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>E1FE00772</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>UNIT-A</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>表裏判別／除塵部</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>E1ZE01395</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
@@ -4067,19 +3781,17 @@
         </is>
       </c>
       <c r="T51" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="n">
-        <v>374.444</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
     </row>
@@ -4087,23 +3799,45 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>14A</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="H52" t="n">
+        <v>51</v>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>E1DE01368</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>CNVR-A</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>集積コンベヤ</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>E1ZE01397</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
@@ -4112,17 +3846,17 @@
         </is>
       </c>
       <c r="T52" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
+      <c r="AA52" t="n">
+        <v>306.73</v>
+      </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr"/>
     </row>
@@ -4137,25 +3871,23 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>14A</t>
+          <t>14B</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="H53" t="n">
+        <v>52</v>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>E1DE01368</t>
+          <t>E1DE01369</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>CNVR-A</t>
+          <t>HNDLR-A</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -4163,12 +3895,12 @@
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>集積コンベヤ</t>
+          <t>スライド集積移載本体</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>E1ZE01397</t>
+          <t>E1ZE01399</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr"/>
@@ -4179,18 +3911,16 @@
         </is>
       </c>
       <c r="T53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="n">
-        <v>306.73</v>
-      </c>
+      <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>500.6</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr"/>
@@ -4206,25 +3936,23 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>14B</t>
+          <t>14C</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="H54" t="n">
+        <v>53</v>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>E1DE01369</t>
+          <t>E1DE01370</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>HNDLR-A</t>
+          <t>HEAD-A</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -4232,12 +3960,12 @@
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
-          <t>スライド集積移載本体</t>
+          <t>スライド集積移載ヘッド</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>E1ZE01399</t>
+          <t>E1ZE01401</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr"/>
@@ -4248,18 +3976,16 @@
         </is>
       </c>
       <c r="T54" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="n">
-        <v>500.6</v>
-      </c>
+      <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>365.69</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr"/>
@@ -4275,25 +4001,23 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14C</t>
+          <t>14D</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="H55" t="n">
+        <v>54</v>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>E1DE01370</t>
+          <t>E1DE01371</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>HEAD-A</t>
+          <t>SIFTR-A</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -4301,12 +4025,12 @@
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>スライド集積移載ヘッド</t>
+          <t>完成品スライド集積</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>E1ZE01401</t>
+          <t>E1ZE01403</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr"/>
@@ -4317,18 +4041,16 @@
         </is>
       </c>
       <c r="T55" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="n">
-        <v>365.69</v>
-      </c>
+      <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1436.42</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr"/>
@@ -4337,47 +4059,21 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>14D</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="H56" t="n">
+        <v>55</v>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>E1DE01371</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>SIFTR-A</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>完成品スライド集積</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>E1ZE01403</t>
-        </is>
-      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
@@ -4386,19 +4082,17 @@
         </is>
       </c>
       <c r="T56" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="n">
-        <v>1436.42</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA56" t="inlineStr"/>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr"/>
     </row>
@@ -4410,10 +4104,8 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="H57" t="n">
+        <v>56</v>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -4431,7 +4123,7 @@
         </is>
       </c>
       <c r="T57" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
@@ -4453,10 +4145,8 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
+      <c r="H58" t="n">
+        <v>57</v>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -4474,7 +4164,7 @@
         </is>
       </c>
       <c r="T58" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
@@ -4496,10 +4186,8 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="H59" t="n">
+        <v>58</v>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -4517,7 +4205,7 @@
         </is>
       </c>
       <c r="T59" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
@@ -4539,10 +4227,8 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="H60" t="n">
+        <v>59</v>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
@@ -4560,7 +4246,7 @@
         </is>
       </c>
       <c r="T60" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr"/>
@@ -4582,10 +4268,8 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="H61" t="n">
+        <v>60</v>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
@@ -4603,7 +4287,7 @@
         </is>
       </c>
       <c r="T61" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
@@ -4621,23 +4305,45 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>02A</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="H62" t="n">
+        <v>61</v>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>E1DE01372</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>DRIVE-A</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>原動部</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>E1ZE01406</t>
+        </is>
+      </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
@@ -4646,17 +4352,17 @@
         </is>
       </c>
       <c r="T62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
+      <c r="AA62" t="n">
+        <v>426.52</v>
+      </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
     </row>
@@ -4671,25 +4377,23 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>02A</t>
+          <t>02B</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="H63" t="n">
+        <v>62</v>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>E1DE01372</t>
+          <t>E1FE01312</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>DRIVE-A</t>
+          <t>G.BOX-A</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -4697,12 +4401,12 @@
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>原動部</t>
+          <t>原動部G-BOX</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>E1ZE01406</t>
+          <t>E1ZE02082</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr"/>
@@ -4713,18 +4417,16 @@
         </is>
       </c>
       <c r="T63" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="n">
-        <v>426.52</v>
-      </c>
+      <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>303.725</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr"/>
@@ -4740,25 +4442,23 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>02B</t>
+          <t>03A</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="H64" t="n">
+        <v>63</v>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>E1FE01312</t>
+          <t>E1DE01373</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>G.BOX-A</t>
+          <t>CAMS-A</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4766,12 +4466,12 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>原動部G-BOX</t>
+          <t>カム軸配置チェイン駆動部</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>E1ZE02082</t>
+          <t>E1ZE01411</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr"/>
@@ -4782,18 +4482,16 @@
         </is>
       </c>
       <c r="T64" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="n">
-        <v>303.725</v>
-      </c>
+      <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1812.765</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr"/>
@@ -4809,25 +4507,23 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>03A</t>
+          <t>04A</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="H65" t="n">
+        <v>64</v>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>E1DE01373</t>
+          <t>E1DE01376</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>CAMS-A</t>
+          <t>KUDO-A</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4835,12 +4531,12 @@
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
-          <t>カム軸配置チェイン駆動部</t>
+          <t>駆動部:平面図:下面</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>E1ZE01411</t>
+          <t>E1ZE01416</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr"/>
@@ -4851,18 +4547,16 @@
         </is>
       </c>
       <c r="T65" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="n">
-        <v>1812.765</v>
-      </c>
+      <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1985.005</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr"/>
@@ -4883,15 +4577,13 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="H66" t="n">
+        <v>65</v>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>E1DE01376</t>
+          <t>E1DE01377</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4904,12 +4596,12 @@
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
-          <t>駆動部:平面図:下面</t>
+          <t>駆動部:平面図:上面/裏面</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>E1ZE01416</t>
+          <t>E1ZE01417</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr"/>
@@ -4920,18 +4612,16 @@
         </is>
       </c>
       <c r="T66" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="n">
-        <v>1985.005</v>
-      </c>
+      <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1985.005</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr"/>
@@ -4952,15 +4642,13 @@
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="H67" t="n">
+        <v>66</v>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>E1DE01377</t>
+          <t>E1DE01378</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4973,12 +4661,12 @@
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>駆動部:平面図:上面/裏面</t>
+          <t>駆動部:側面図:A-D</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>E1ZE01417</t>
+          <t>E1ZE01418</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr"/>
@@ -4989,18 +4677,16 @@
         </is>
       </c>
       <c r="T67" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="n">
-        <v>1985.005</v>
-      </c>
+      <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1985.005</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr"/>
@@ -5021,15 +4707,13 @@
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="H68" t="n">
+        <v>67</v>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>E1DE01378</t>
+          <t>E1DE01379</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5042,12 +4726,12 @@
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
-          <t>駆動部:側面図:A-D</t>
+          <t>駆動部:側面図:E-H</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>E1ZE01418</t>
+          <t>E1ZE01419</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr"/>
@@ -5058,18 +4742,16 @@
         </is>
       </c>
       <c r="T68" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="n">
-        <v>1985.005</v>
-      </c>
+      <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1985.005</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr"/>
@@ -5090,15 +4772,13 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="H69" t="n">
+        <v>68</v>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>E1DE01379</t>
+          <t>E1DE01380</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -5111,12 +4791,12 @@
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
-          <t>駆動部:側面図:E-H</t>
+          <t>駆動部:側面図:I-J</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>E1ZE01419</t>
+          <t>E1ZE01420</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr"/>
@@ -5127,18 +4807,16 @@
         </is>
       </c>
       <c r="T69" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="n">
-        <v>1985.005</v>
-      </c>
+      <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1985.005</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr"/>
@@ -5147,47 +4825,21 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>04A</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="H70" t="n">
+        <v>69</v>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>E1DE01380</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>KUDO-A</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>駆動部:側面図:I-J</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>E1ZE01420</t>
-        </is>
-      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
@@ -5196,19 +4848,17 @@
         </is>
       </c>
       <c r="T70" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="n">
-        <v>1985.005</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA70" t="inlineStr"/>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr"/>
     </row>
@@ -5220,10 +4870,8 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="H71" t="n">
+        <v>70</v>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -5241,7 +4889,7 @@
         </is>
       </c>
       <c r="T71" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
@@ -5263,10 +4911,8 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="H72" t="n">
+        <v>71</v>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
@@ -5284,7 +4930,7 @@
         </is>
       </c>
       <c r="T72" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
@@ -5306,10 +4952,8 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
+      <c r="H73" t="n">
+        <v>72</v>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
@@ -5327,7 +4971,7 @@
         </is>
       </c>
       <c r="T73" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
@@ -5349,10 +4993,8 @@
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="H74" t="n">
+        <v>73</v>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
@@ -5370,7 +5012,7 @@
         </is>
       </c>
       <c r="T74" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
@@ -5392,10 +5034,8 @@
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="H75" t="n">
+        <v>74</v>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
@@ -5413,7 +5053,7 @@
         </is>
       </c>
       <c r="T75" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
@@ -5435,10 +5075,8 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="H76" t="n">
+        <v>75</v>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
@@ -5456,7 +5094,7 @@
         </is>
       </c>
       <c r="T76" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
@@ -5474,23 +5112,45 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>05B</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="H77" t="n">
+        <v>76</v>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>E1DE02304</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>AIR-A</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>エア機器配置図上面</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>E1ZE02035</t>
+        </is>
+      </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
@@ -5499,17 +5159,17 @@
         </is>
       </c>
       <c r="T77" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
+      <c r="AA77" t="n">
+        <v>1872.949</v>
+      </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr"/>
     </row>
@@ -5529,15 +5189,13 @@
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+      <c r="H78" t="n">
+        <v>77</v>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>E1DE02304</t>
+          <t>E1DE02305</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5550,12 +5208,12 @@
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
-          <t>エア機器配置図上面</t>
+          <t>エア機器配置図下面</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>E1ZE02035</t>
+          <t>E1ZE02036</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr"/>
@@ -5566,18 +5224,16 @@
         </is>
       </c>
       <c r="T78" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="n">
-        <v>1872.949</v>
-      </c>
+      <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1872.949</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr"/>
@@ -5593,25 +5249,23 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>05B</t>
+          <t>05D</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
+      <c r="H79" t="n">
+        <v>78</v>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
-          <t>E1DE02305</t>
+          <t>E1DE01385</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>AIR-A</t>
+          <t>DUCT-A</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -5619,12 +5273,12 @@
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
-          <t>エア機器配置図下面</t>
+          <t>集塵配管図</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>E1ZE02036</t>
+          <t>E1ZE01439</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr"/>
@@ -5635,18 +5289,16 @@
         </is>
       </c>
       <c r="T79" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="n">
-        <v>1872.949</v>
-      </c>
+      <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>123.174</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr"/>
@@ -5662,25 +5314,23 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>05D</t>
+          <t>05C</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+      <c r="H80" t="n">
+        <v>79</v>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>E1DE01385</t>
+          <t>E1DE02073</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>DUCT-A</t>
+          <t>OIL-A</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -5688,12 +5338,12 @@
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
-          <t>集塵配管図</t>
+          <t>給脂・給油配管図</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>E1ZE01439</t>
+          <t>E1ZE02083</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr"/>
@@ -5704,18 +5354,16 @@
         </is>
       </c>
       <c r="T80" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="n">
-        <v>123.174</v>
-      </c>
+      <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>296.586</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr"/>
@@ -5724,47 +5372,21 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>05C</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
+      <c r="H81" t="n">
+        <v>80</v>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>E1DE02073</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>OIL-A</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>給脂・給油配管図</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>E1ZE02083</t>
-        </is>
-      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
@@ -5773,19 +5395,17 @@
         </is>
       </c>
       <c r="T81" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="n">
-        <v>296.586</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr"/>
     </row>
@@ -5793,23 +5413,45 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>01H</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="H82" t="n">
+        <v>81</v>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>E1DE02063</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>B/M-A</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>ベースマシン</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>E1ZE01425</t>
+        </is>
+      </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
@@ -5818,17 +5460,17 @@
         </is>
       </c>
       <c r="T82" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
+      <c r="AA82" t="n">
+        <v>530.5</v>
+      </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr"/>
     </row>
@@ -5843,25 +5485,23 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>01H</t>
+          <t>06A</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="H83" t="n">
+        <v>82</v>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>E1DE02063</t>
+          <t>E1DE01388</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>B/M-A</t>
+          <t>CV-A</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5869,14 +5509,10 @@
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
-          <t>ベースマシン</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>E1ZE01425</t>
-        </is>
-      </c>
+          <t>マシンカバー</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
@@ -5885,18 +5521,16 @@
         </is>
       </c>
       <c r="T83" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="n">
-        <v>530.5</v>
-      </c>
+      <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>348.493</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr"/>
@@ -5912,20 +5546,18 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>06A</t>
+          <t>06B</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="H84" t="n">
+        <v>83</v>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>E1DE01388</t>
+          <t>E1DE02068</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5938,10 +5570,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>マシンカバー</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
+          <t>安全カバー:1</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>E1ZE02071</t>
+        </is>
+      </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
@@ -5950,18 +5586,16 @@
         </is>
       </c>
       <c r="T84" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="n">
-        <v>348.493</v>
-      </c>
+      <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1711.734</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr"/>
@@ -5982,15 +5616,13 @@
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="H85" t="n">
+        <v>84</v>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>E1DE02068</t>
+          <t>E1DE01390</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6003,12 +5635,12 @@
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
-          <t>安全カバー:1</t>
+          <t>安全カバー:2</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>E1ZE02071</t>
+          <t>E1ZE01624</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr"/>
@@ -6019,18 +5651,16 @@
         </is>
       </c>
       <c r="T85" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="n">
-        <v>1711.734</v>
-      </c>
+      <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1711.734</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="inlineStr"/>
@@ -6051,15 +5681,13 @@
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="H86" t="n">
+        <v>85</v>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>E1DE01390</t>
+          <t>E1DE01391</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -6072,12 +5700,12 @@
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>安全カバー:2</t>
+          <t>安全カバー:3</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>E1ZE01624</t>
+          <t>E1ZE01628</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr"/>
@@ -6088,18 +5716,16 @@
         </is>
       </c>
       <c r="T86" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U86" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="n">
-        <v>1711.734</v>
-      </c>
+      <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1711.734</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr"/>
@@ -6115,25 +5741,23 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>06B</t>
+          <t>07A</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="H87" t="n">
+        <v>86</v>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>E1DE01391</t>
+          <t>E1FE00775</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>CV-A</t>
+          <t>PANEL-A</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6141,12 +5765,12 @@
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
-          <t>安全カバー:3</t>
+          <t>主操作盤取付</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>E1ZE01628</t>
+          <t>E1ZE01444</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr"/>
@@ -6157,18 +5781,16 @@
         </is>
       </c>
       <c r="T87" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="n">
-        <v>1711.734</v>
-      </c>
+      <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>113.311</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="inlineStr"/>
@@ -6184,20 +5806,18 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>07A</t>
+          <t>07B</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="H88" t="n">
+        <v>87</v>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>E1FE00775</t>
+          <t>E1FE00776</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6210,12 +5830,12 @@
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
-          <t>主操作盤取付</t>
+          <t>副操作盤取付</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>E1ZE01444</t>
+          <t>E1ZE01445</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr"/>
@@ -6226,15 +5846,13 @@
         </is>
       </c>
       <c r="T88" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="U88" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="n">
-        <v>113.311</v>
-      </c>
+      <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="n">
         <v>0</v>
@@ -6253,25 +5871,23 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>07B</t>
+          <t>07C</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
+      <c r="H89" t="n">
+        <v>88</v>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
-          <t>E1FE00776</t>
+          <t>E1FE00777</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>PANEL-A</t>
+          <t>DUCT-A</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -6279,12 +5895,12 @@
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
-          <t>副操作盤取付</t>
+          <t>配線ダクト</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>E1ZE01445</t>
+          <t>E1ZE01447</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr"/>
@@ -6295,7 +5911,7 @@
         </is>
       </c>
       <c r="T89" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
@@ -6304,7 +5920,7 @@
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>224.333</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="inlineStr"/>
@@ -6320,25 +5936,23 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>07C</t>
+          <t>07D</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
+      <c r="H90" t="n">
+        <v>89</v>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>E1FE00777</t>
+          <t>E1DE02180</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>DUCT-A</t>
+          <t>DEVIC-A</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -6346,12 +5960,12 @@
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
-          <t>配線ダクト</t>
+          <t>デバイス配置図</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>E1ZE01447</t>
+          <t>E1ZE02156</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr"/>
@@ -6362,18 +5976,16 @@
         </is>
       </c>
       <c r="T90" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="n">
-        <v>224.333</v>
-      </c>
+      <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="inlineStr"/>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1042.299</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr"/>
@@ -6382,47 +5994,21 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>07D</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
+      <c r="H91" t="n">
+        <v>90</v>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>E1DE02180</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>DEVIC-A</t>
-        </is>
-      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>デバイス配置図</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>E1ZE02156</t>
-        </is>
-      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
@@ -6431,19 +6017,17 @@
         </is>
       </c>
       <c r="T91" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="n">
-        <v>1042.299</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="inlineStr"/>
-      <c r="AA91" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA91" t="inlineStr"/>
       <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="inlineStr"/>
     </row>
@@ -6451,22 +6035,40 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>(0)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>04F</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="H92" t="n">
+        <v>91</v>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>E1FE00778</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>CHART-A</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>タイミングチャート</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -6476,15 +6078,13 @@
         </is>
       </c>
       <c r="T92" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr"/>
       <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr"/>
@@ -6501,25 +6101,23 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>04F</t>
+          <t>05A</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
+      <c r="H93" t="n">
+        <v>92</v>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
-          <t>E1FE00778</t>
+          <t>E1DE02044</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>CHART-A</t>
+          <t>AIR.S</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -6527,7 +6125,7 @@
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
-          <t>タイミングチャート</t>
+          <t>エア回路図</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
@@ -6539,7 +6137,7 @@
         </is>
       </c>
       <c r="T93" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
@@ -6560,27 +6158,21 @@
           <t>(0)</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>05A</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="H94" t="n">
+        <v>93</v>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
-          <t>E1DE02044</t>
+          <t>E1DE01396</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>AIR.S</t>
+          <t>UTY-A</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -6588,7 +6180,7 @@
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
-          <t>エア回路図</t>
+          <t>ユーティリティ接続図</t>
         </is>
       </c>
       <c r="P94" t="inlineStr"/>
@@ -6600,7 +6192,7 @@
         </is>
       </c>
       <c r="T94" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
@@ -6618,26 +6210,24 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>(0)</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="H95" t="n">
+        <v>94</v>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>E1DE01396</t>
+          <t>E1FE01323</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>UTY-A</t>
+          <t>LABEL-A</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -6645,7 +6235,7 @@
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
-          <t>ユーティリティ接続図</t>
+          <t>銘板/警告ラベル貼付図</t>
         </is>
       </c>
       <c r="P95" t="inlineStr"/>
@@ -6657,7 +6247,7 @@
         </is>
       </c>
       <c r="T95" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
@@ -6665,7 +6255,9 @@
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
+      <c r="AA95" t="n">
+        <v>0</v>
+      </c>
       <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="inlineStr"/>
     </row>
@@ -6673,38 +6265,20 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>1A</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
+      <c r="H96" t="n">
+        <v>95</v>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>E1FE01323</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>LABEL-A</t>
-        </is>
-      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>銘板/警告ラベル貼付図</t>
-        </is>
-      </c>
+      <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -6714,17 +6288,17 @@
         </is>
       </c>
       <c r="T96" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
       <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA96" t="inlineStr"/>
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr"/>
     </row>
@@ -6736,10 +6310,8 @@
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="H97" t="n">
+        <v>96</v>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
@@ -6757,7 +6329,7 @@
         </is>
       </c>
       <c r="T97" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
@@ -6779,10 +6351,8 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
+      <c r="H98" t="n">
+        <v>97</v>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
@@ -6800,7 +6370,7 @@
         </is>
       </c>
       <c r="T98" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
@@ -6818,23 +6388,45 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>01J</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
+      <c r="H99" t="n">
+        <v>98</v>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>E1DE01397</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>UNPAN-A</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>運搬解体図</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>E1ZE01446</t>
+        </is>
+      </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
@@ -6843,17 +6435,17 @@
         </is>
       </c>
       <c r="T99" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr"/>
+      <c r="AA99" t="n">
+        <v>0.352</v>
+      </c>
       <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr"/>
     </row>
@@ -6868,25 +6460,23 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>01J</t>
+          <t>01G</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+      <c r="H100" t="n">
+        <v>99</v>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
-          <t>E1DE01397</t>
+          <t>E1FE01366</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>UNPAN-A</t>
+          <t>JIG-A</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -6894,12 +6484,12 @@
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>運搬解体図</t>
+          <t>芯出し</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>E1ZE01446</t>
+          <t>E1ZE02172</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr"/>
@@ -6910,18 +6500,16 @@
         </is>
       </c>
       <c r="T100" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="n">
-        <v>0.352</v>
-      </c>
+      <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>72.423</v>
       </c>
       <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr"/>
@@ -6932,30 +6520,24 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1A</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>01G</t>
-        </is>
-      </c>
+          <t>(0)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
+      <c r="H101" t="n">
+        <v>100</v>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>E1FE01366</t>
+          <t>E1DE02148</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>JIG-A</t>
+          <t>GENRL-A</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -6963,14 +6545,10 @@
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
-          <t>芯出し</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>E1ZE02172</t>
-        </is>
-      </c>
+          <t>全体図</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
@@ -6979,19 +6557,15 @@
         </is>
       </c>
       <c r="T101" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr"/>
-      <c r="Y101" t="n">
-        <v>72.423</v>
-      </c>
+      <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
-      <c r="AA101" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA101" t="inlineStr"/>
       <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="inlineStr"/>
     </row>
@@ -6999,49 +6573,23 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>(0)</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>E1DE02148</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>GENRL-A</t>
-        </is>
-      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>全体図</t>
-        </is>
-      </c>
+      <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>E1ZE02-133</t>
-        </is>
-      </c>
-      <c r="T102" t="n">
-        <v>100</v>
-      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr"/>
@@ -7062,13 +6610,25 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>SHH512310</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>SAM-11全体図</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>SHM521143</t>
+        </is>
+      </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr"/>
@@ -7095,7 +6655,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
-          <t>SHH512310</t>
+          <t>SHH215905</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -7104,12 +6664,12 @@
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
-          <t>SAM-11全体図</t>
+          <t>SAM-12全体図</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>SHM521143</t>
+          <t>SHM220246</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr"/>
@@ -7138,7 +6698,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t>SHH215905</t>
+          <t>E1DE00204</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -7147,12 +6707,12 @@
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
-          <t>SAM-12全体図</t>
+          <t>SAM-13全体図</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>SHM220246</t>
+          <t>E1ZE00277</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr"/>
@@ -7181,7 +6741,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>E1DE00204</t>
+          <t>E1DE01008</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -7190,12 +6750,12 @@
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>SAM-13全体図</t>
+          <t>SAM-14全体図</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>E1ZE00277</t>
+          <t>E1ZE00990</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr"/>
@@ -7224,7 +6784,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>E1DE01008</t>
+          <t>E1DE01328</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -7233,12 +6793,12 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>SAM-14全体図</t>
+          <t>SAM-15全体図</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>E1ZE00990</t>
+          <t>E1ZE01303</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr"/>
@@ -7267,7 +6827,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
-          <t>E1DE01328</t>
+          <t>E1DE02103</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7276,12 +6836,12 @@
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>SAM-15全体図</t>
+          <t>SAM-16全体図</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>E1ZE01303</t>
+          <t>E1ZE02110</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr"/>
@@ -7310,7 +6870,7 @@
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
-          <t>E1DE02103</t>
+          <t>E1DE02148</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7319,12 +6879,12 @@
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>SAM-16全体図</t>
+          <t>SAM-18全体図</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>E1ZE02110</t>
+          <t>E1ZE02133</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr"/>
@@ -7351,25 +6911,13 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>E1DE02148</t>
-        </is>
-      </c>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>SAM-18全体図</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>E1ZE02133</t>
-        </is>
-      </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr"/>
@@ -7394,7 +6942,9 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+      <c r="J111" t="n">
+        <v>80</v>
+      </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
@@ -7415,39 +6965,6 @@
       <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="inlineStr"/>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="n">
-        <v>80</v>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
-      <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
-      <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
-      <c r="AB112" t="inlineStr"/>
-      <c r="AC112" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
